--- a/data/trans_orig/Q5410-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -846,82 +846,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>857</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7080</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107909</t>
+          <t>107956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>114136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141474</t>
+          <t>141667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253519</t>
+          <t>253498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262786</t>
+          <t>262787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8325</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1224</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4997</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6125</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138228</t>
+          <t>138238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145028</t>
+          <t>145032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165522</t>
+          <t>165043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178960</t>
+          <t>178636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>307886</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322803</t>
+          <t>322763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99964</t>
+          <t>99897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128146</t>
+          <t>126167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>134817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230356</t>
+          <t>230673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239097</t>
+          <t>239172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132156</t>
+          <t>131390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191460</t>
+          <t>190600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204426</t>
+          <t>204146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>325830</t>
+          <t>325352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>340159</t>
+          <t>340373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>486727</t>
+          <t>488130</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>498058</t>
+          <t>498253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>641032</t>
+          <t>640852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>661291</t>
+          <t>661170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1134200</t>
+          <t>1133421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1156736</t>
+          <t>1157292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130998</t>
+          <t>131054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138505</t>
+          <t>139357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152659</t>
+          <t>152227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163576</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>286873</t>
+          <t>288073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>300935</t>
+          <t>300924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139184</t>
+          <t>139036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150799</t>
+          <t>150647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169481</t>
+          <t>170354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183891</t>
+          <t>183897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312271</t>
+          <t>313872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332039</t>
+          <t>332817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89662</t>
+          <t>89778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102480</t>
+          <t>102455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124176</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137613</t>
+          <t>137464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219117</t>
+          <t>218806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237184</t>
+          <t>237020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145802</t>
+          <t>146244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158590</t>
+          <t>158644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>223773</t>
+          <t>223915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>237447</t>
+          <t>238357</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>376026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>393775</t>
+          <t>393958</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39953</t>
+          <t>39621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522180</t>
+          <t>524191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>543702</t>
+          <t>544707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>684793</t>
+          <t>686967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>712782</t>
+          <t>713631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1219192</t>
+          <t>1217257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1252618</t>
+          <t>1251653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>124945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134202</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159690</t>
+          <t>158928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171018</t>
+          <t>170463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>287935</t>
+          <t>289247</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302726</t>
+          <t>303395</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153099</t>
+          <t>153569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>162377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205709</t>
+          <t>205471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217867</t>
+          <t>217836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363293</t>
+          <t>362944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378162</t>
+          <t>377884</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6669,97 +6669,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8459</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2618</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8937</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7944</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>9309</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106616</t>
+          <t>106803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114222</t>
+          <t>114136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131273</t>
+          <t>131285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141304</t>
+          <t>141314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241587</t>
+          <t>241872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253945</t>
+          <t>253887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -7125,82 +7125,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1233</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6272</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167627</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228497</t>
+          <t>228628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240322</t>
+          <t>240287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>400720</t>
+          <t>400991</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>414152</t>
+          <t>413697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>564430</t>
+          <t>565250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>580273</t>
+          <t>580081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>740948</t>
+          <t>742830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>763074</t>
+          <t>763494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1313182</t>
+          <t>1313810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1339618</t>
+          <t>1340273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,47 +8284,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1622</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1622</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3869</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>142089</t>
+          <t>141771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146854</t>
+          <t>146675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165301</t>
+          <t>165460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173038</t>
+          <t>173080</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>309452</t>
+          <t>309324</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>318692</t>
+          <t>318339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152175</t>
+          <t>151813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158371</t>
+          <t>158236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200582</t>
+          <t>200543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210313</t>
+          <t>210194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355856</t>
+          <t>355426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367407</t>
+          <t>367058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -9181,97 +9181,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7692</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1673</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7657</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6660</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128909</t>
+          <t>128054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135659</t>
+          <t>135438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337963</t>
+          <t>339173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359074</t>
+          <t>359531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>474839</t>
+          <t>474580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>494637</t>
+          <t>494411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>197027</t>
+          <t>196863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256081</t>
+          <t>255391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266739</t>
+          <t>266775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>455507</t>
+          <t>455715</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>468484</t>
+          <t>468292</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22363</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42867</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>628893</t>
+          <t>627740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>640245</t>
+          <t>639778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>974870</t>
+          <t>975036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1008764</t>
+          <t>1011681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1608970</t>
+          <t>1611057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1644045</t>
+          <t>1645514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107956</t>
+          <t>108772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114136</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141667</t>
+          <t>141728</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253498</t>
+          <t>253665</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262787</t>
+          <t>262769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,47 +1352,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>10376</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>18125</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>10376</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>19131</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138238</t>
+          <t>138002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145032</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165043</t>
+          <t>164729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178636</t>
+          <t>179110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>308166</t>
+          <t>307570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322763</t>
+          <t>322529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99897</t>
+          <t>99830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126167</t>
+          <t>126760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134817</t>
+          <t>134822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230673</t>
+          <t>230941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239172</t>
+          <t>239171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,47 +2136,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8796</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131390</t>
+          <t>132197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190600</t>
+          <t>190253</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204146</t>
+          <t>203424</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>325352</t>
+          <t>326270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>340373</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488130</t>
+          <t>487510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>498253</t>
+          <t>498172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>640852</t>
+          <t>639905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>661170</t>
+          <t>661311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1133421</t>
+          <t>1133097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1157292</t>
+          <t>1156210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131054</t>
+          <t>130945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139357</t>
+          <t>138562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152227</t>
+          <t>152561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163554</t>
+          <t>163564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>288073</t>
+          <t>286839</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>300924</t>
+          <t>301002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139036</t>
+          <t>138684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150647</t>
+          <t>150798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170354</t>
+          <t>169366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183897</t>
+          <t>183912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>313872</t>
+          <t>313761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332817</t>
+          <t>332198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89778</t>
+          <t>88999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102455</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>123950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137464</t>
+          <t>137530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218806</t>
+          <t>220093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237020</t>
+          <t>237322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146244</t>
+          <t>146261</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158644</t>
+          <t>158630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>223915</t>
+          <t>224600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>238357</t>
+          <t>238394</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>376026</t>
+          <t>376162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>393958</t>
+          <t>394156</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>31211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39621</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>524191</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>544707</t>
+          <t>543920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>686967</t>
+          <t>689004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>713631</t>
+          <t>714049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1217257</t>
+          <t>1219230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1251653</t>
+          <t>1252825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124945</t>
+          <t>124696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134229</t>
+          <t>134156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158928</t>
+          <t>159861</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170463</t>
+          <t>171050</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>289247</t>
+          <t>288962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>303395</t>
+          <t>303282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153569</t>
+          <t>152697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162377</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205471</t>
+          <t>205220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217836</t>
+          <t>217156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362944</t>
+          <t>363564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377884</t>
+          <t>377895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106803</t>
+          <t>106397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114136</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131285</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141314</t>
+          <t>141302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241872</t>
+          <t>240491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253887</t>
+          <t>253586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167822</t>
+          <t>167113</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228628</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240287</t>
+          <t>240253</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>400991</t>
+          <t>401330</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>413697</t>
+          <t>413960</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>565250</t>
+          <t>563887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>580081</t>
+          <t>580085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>742830</t>
+          <t>741490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>763494</t>
+          <t>763083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1313810</t>
+          <t>1314356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1340273</t>
+          <t>1340697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>144980</t>
+          <t>160211</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141771</t>
+          <t>156984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146675</t>
+          <t>161921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>169690</t>
+          <t>180927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165460</t>
+          <t>175690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173080</t>
+          <t>184332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>314669</t>
+          <t>341138</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>309324</t>
+          <t>335371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>318339</t>
+          <t>345024</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>178667</t>
+          <t>190426</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178667</t>
+          <t>190426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178667</t>
+          <t>190426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>326749</t>
+          <t>353740</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>326749</t>
+          <t>353740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326749</t>
+          <t>353740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8833,27 +8833,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>173856</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151813</t>
+          <t>169598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158236</t>
+          <t>176462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,17 +8981,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>206052</t>
+          <t>227991</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200543</t>
+          <t>221779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210194</t>
+          <t>232885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>362071</t>
+          <t>401846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355426</t>
+          <t>395072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367058</t>
+          <t>407745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133267</t>
+          <t>155620</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128054</t>
+          <t>150649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135438</t>
+          <t>158375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>352261</t>
+          <t>166036</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339173</t>
+          <t>159583</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359531</t>
+          <t>169997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>485529</t>
+          <t>321657</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>474580</t>
+          <t>315135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>494411</t>
+          <t>326962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>498</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>200824</t>
+          <t>210675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196863</t>
+          <t>206810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203174</t>
+          <t>213104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>262194</t>
+          <t>279890</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>255391</t>
+          <t>271502</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266775</t>
+          <t>285161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>463018</t>
+          <t>490564</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>455715</t>
+          <t>482396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>468292</t>
+          <t>497077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>509801</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>509801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>509801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>59237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>635090</t>
+          <t>700361</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>627740</t>
+          <t>693034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>639778</t>
+          <t>705665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>990196</t>
+          <t>854843</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>975036</t>
+          <t>843069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1011681</t>
+          <t>864204</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1625287</t>
+          <t>1555204</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1611057</t>
+          <t>1542681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1645514</t>
+          <t>1565827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
